--- a/assets/libreoffice_calc_njc/32faea23-58b3-471f-957a-f8798afde48a/Product_Name_Clean.xlsx
+++ b/assets/libreoffice_calc_njc/32faea23-58b3-471f-957a-f8798afde48a/Product_Name_Clean.xlsx
@@ -164,8 +164,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -187,256 +191,256 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:D21"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="str">
+      <c r="C2" s="1" t="str">
         <f aca="false">PROPER(TRIM(B2))</f>
         <v>Laptop Pro</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>149.99</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="0" t="str">
+      <c r="C3" s="1" t="str">
         <f aca="false">PROPER(TRIM(B3))</f>
         <v>Wireless Mouse</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>29.99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="str">
+      <c r="C4" s="1" t="str">
         <f aca="false">PROPER(TRIM(B4))</f>
         <v>Mechanical Keyboard</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>79.99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="0" t="str">
+      <c r="C5" s="1" t="str">
         <f aca="false">PROPER(TRIM(B5))</f>
         <v>Usb-C Hub</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>45.99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="0" t="str">
+      <c r="C6" s="1" t="str">
         <f aca="false">PROPER(TRIM(B6))</f>
         <v>Bluetooth Speaker</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>59.99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="0" t="str">
+      <c r="C7" s="1" t="str">
         <f aca="false">PROPER(TRIM(B7))</f>
         <v>Noise Cancelling Headphones</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>149.99</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="0" t="str">
+      <c r="C8" s="1" t="str">
         <f aca="false">PROPER(TRIM(B8))</f>
         <v>4K Monitor</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>299.99</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="0" t="str">
+      <c r="C9" s="1" t="str">
         <f aca="false">PROPER(TRIM(B9))</f>
         <v>Portable Ssd</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>89.99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="0" t="str">
+      <c r="C10" s="1" t="str">
         <f aca="false">PROPER(TRIM(B10))</f>
         <v>Webcam Hd</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>49.99</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="0" t="str">
+      <c r="C11" s="1" t="str">
         <f aca="false">PROPER(TRIM(B11))</f>
         <v>Smartwatch</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>199.99</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="0" t="str">
+      <c r="C12" s="1" t="str">
         <f aca="false">PROPER(TRIM(B12))</f>
         <v>Gaming Chair</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>349.99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="0" t="str">
+      <c r="C13" s="1" t="str">
         <f aca="false">PROPER(TRIM(B13))</f>
         <v>Desk Lamp</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>35.99</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="0" t="str">
+      <c r="C14" s="1" t="str">
         <f aca="false">PROPER(TRIM(B14))</f>
         <v>Standing Desk</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <v>499.99</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="0" t="str">
+      <c r="C15" s="1" t="str">
         <f aca="false">PROPER(TRIM(B15))</f>
         <v>Wireless Charger</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>39.99</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="0" t="str">
+      <c r="C16" s="1" t="str">
         <f aca="false">PROPER(TRIM(B16))</f>
         <v>Screen Protector</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <v>12.99</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="0" t="str">
+      <c r="C17" s="1" t="str">
         <f aca="false">PROPER(TRIM(B17))</f>
         <v>Cable Organizer</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <v>18.99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="0" t="str">
+      <c r="C18" s="1" t="str">
         <f aca="false">PROPER(TRIM(B18))</f>
         <v>Laptop Stand</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="1" t="n">
         <v>54.99</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="0" t="str">
+      <c r="C19" s="1" t="str">
         <f aca="false">PROPER(TRIM(B19))</f>
         <v>Monitor Arm</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="1" t="n">
         <v>89.99</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="0" t="str">
+      <c r="C20" s="1" t="str">
         <f aca="false">PROPER(TRIM(B20))</f>
         <v>Ergonomic Mouse Pad</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="1" t="n">
         <v>24.99</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="0" t="str">
+      <c r="C21" s="1" t="str">
         <f aca="false">PROPER(TRIM(B21))</f>
         <v>Cable Management Box</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21" s="1" t="n">
         <v>29.99</v>
       </c>
     </row>
